--- a/Assets/Data/Excel/QuestTable.xlsx
+++ b/Assets/Data/Excel/QuestTable.xlsx
@@ -1,45 +1,152 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\Work\UnityProject\MadHatter\Assets\Data\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B612CAA3-49C3-4435-99C6-B298BE3D09F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QuestTable" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="QuestTable" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+  <si>
+    <t>uniqueId</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>goalType</t>
+  </si>
+  <si>
+    <t>goalCount</t>
+  </si>
+  <si>
+    <t>questGiverNpcId</t>
+  </si>
+  <si>
+    <t>startDialogueId</t>
+  </si>
+  <si>
+    <t>progressDialogueId</t>
+  </si>
+  <si>
+    <t>completedDialogueId</t>
+  </si>
+  <si>
+    <t>nextQuestId</t>
+  </si>
+  <si>
+    <t>rewardGroupId</t>
+  </si>
+  <si>
+    <t>QST_001</t>
+  </si>
+  <si>
+    <t>이장의 부탁</t>
+  </si>
+  <si>
+    <t>마을 이장의 이야기를 듣고 대장장이를 찾아가자.</t>
+  </si>
+  <si>
+    <t>Talk</t>
+  </si>
+  <si>
+    <t>NPC_001</t>
+  </si>
+  <si>
+    <t>NPC_002</t>
+  </si>
+  <si>
+    <t>DLG_002</t>
+  </si>
+  <si>
+    <t>DLG_003</t>
+  </si>
+  <si>
+    <t>DLG_004</t>
+  </si>
+  <si>
+    <t>QST_002</t>
+  </si>
+  <si>
+    <t>RWD_001</t>
+  </si>
+  <si>
+    <t>대장장이의 고민</t>
+  </si>
+  <si>
+    <t>대장장이의 고민을 듣고 마을 이장에게 전달하자.</t>
+  </si>
+  <si>
+    <t>DLG_005</t>
+  </si>
+  <si>
+    <t>DLG_006</t>
+  </si>
+  <si>
+    <t>DLG_007</t>
+  </si>
+  <si>
+    <t>RWD_002</t>
+  </si>
+  <si>
+    <t>targetId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -52,96 +159,46 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -429,207 +486,137 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>uniqueId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>goalType</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>goalCount</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>questGiverNpcId</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>questCompleterNpcId</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>startDialogueId</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>progressDialogueId</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>completedDialogueId</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>nextQuestId</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>rewardGroupId</t>
-        </is>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>QST_001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>이장의 부탁</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>마을 이장의 이야기를 듣고 대장장이를 찾아가자.</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Talk</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>NPC_001</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>NPC_002</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>DLG_002</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>DLG_003</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>DLG_004</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>QST_002</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>RWD_001</t>
-        </is>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>QST_002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>대장장이의 고민</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>대장장이의 고민을 듣고 마을 이장에게 전달하자.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Talk</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>NPC_002</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>NPC_001</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>DLG_005</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>DLG_006</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>DLG_007</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>RWD_002</t>
-        </is>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Assets/Data/Excel/QuestTable.xlsx
+++ b/Assets/Data/Excel/QuestTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\Work\UnityProject\MadHatter\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B612CAA3-49C3-4435-99C6-B298BE3D09F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445664DE-9DD3-48D4-9F42-FC788EEF5DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="180" windowWidth="28800" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QuestTable" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>uniqueId</t>
   </si>
@@ -40,6 +40,9 @@
     <t>questGiverNpcId</t>
   </si>
   <si>
+    <t>targetId</t>
+  </si>
+  <si>
     <t>startDialogueId</t>
   </si>
   <si>
@@ -103,11 +106,34 @@
     <t>DLG_007</t>
   </si>
   <si>
+    <t>QST_003</t>
+  </si>
+  <si>
     <t>RWD_002</t>
   </si>
   <si>
-    <t>targetId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>슬라임 퇴치</t>
+  </si>
+  <si>
+    <t>마을 근처의 슬라임 1마리를 처치하자.</t>
+  </si>
+  <si>
+    <t>Kill</t>
+  </si>
+  <si>
+    <t>slime_01</t>
+  </si>
+  <si>
+    <t>DLG_010</t>
+  </si>
+  <si>
+    <t>DLG_011</t>
+  </si>
+  <si>
+    <t>DLG_012</t>
+  </si>
+  <si>
+    <t>RWD_003</t>
   </si>
 </sst>
 </file>
@@ -487,11 +513,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="3" max="3" width="56.125" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
@@ -523,96 +549,133 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="L3" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Excel/QuestTable.xlsx
+++ b/Assets/Data/Excel/QuestTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\Work\UnityProject\MadHatter\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445664DE-9DD3-48D4-9F42-FC788EEF5DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E575FAA-93EB-4639-877E-0CFBEF087032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="180" windowWidth="28800" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -121,9 +121,6 @@
     <t>Kill</t>
   </si>
   <si>
-    <t>slime_01</t>
-  </si>
-  <si>
     <t>DLG_010</t>
   </si>
   <si>
@@ -134,6 +131,10 @@
   </si>
   <si>
     <t>RWD_003</t>
+  </si>
+  <si>
+    <t>E_001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -663,19 +664,19 @@
         <v>17</v>
       </c>
       <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" t="s">
         <v>33</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>34</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>35</v>
       </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
         <v>36</v>
-      </c>
-      <c r="L4" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Excel/QuestTable.xlsx
+++ b/Assets/Data/Excel/QuestTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\Work\UnityProject\MadHatter\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E575FAA-93EB-4639-877E-0CFBEF087032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6256D564-E456-4C0C-B9E7-71196653138B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="180" windowWidth="28800" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QuestTable" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
   <si>
     <t>uniqueId</t>
   </si>
@@ -135,6 +135,17 @@
   <si>
     <t>E_001</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>targetDialogueId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DLG_013</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DLG_014</t>
   </si>
 </sst>
 </file>
@@ -164,7 +175,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -174,6 +185,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -204,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -212,6 +235,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -514,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -525,12 +556,12 @@
     <col min="7" max="7" width="23" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="17" customWidth="1"/>
+    <col min="10" max="11" width="23" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,13 +593,16 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -584,29 +618,32 @@
       <c r="E2" s="2">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -622,29 +659,32 @@
       <c r="E3" s="2">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -660,24 +700,129 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L4" t="s">
+      <c r="K4" s="6"/>
+      <c r="M4" t="s">
         <v>36</v>
       </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F5" s="4"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F6" s="4"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F7" s="4"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F8" s="4"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F9" s="4"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F10" s="4"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="6"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F11" s="4"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="6"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F12" s="4"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="6"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F13" s="4"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="6"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F14" s="4"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="6"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F15" s="4"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="6"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F16" s="4"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="6"/>
+    </row>
+    <row r="17" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F17" s="4"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
